--- a/data/trans_bre/P19C01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Provincia-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 18,14</t>
+          <t>-0,36; 17,76</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,35; 5,94</t>
+          <t>-8,66; 5,26</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,93; 15,51</t>
+          <t>-0,66; 15,97</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,19; 4,0</t>
+          <t>-2,45; 3,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 78,28</t>
+          <t>-1,87; 76,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-37,89; 40,21</t>
+          <t>-39,58; 34,61</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-6,85; 80,42</t>
+          <t>-1,88; 80,56</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 4,32</t>
+          <t>-2,54; 4,12</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-6,62; 6,08</t>
+          <t>-7,02; 6,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,0; 7,09</t>
+          <t>-6,45; 6,42</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,67; 13,96</t>
+          <t>0,13; 13,76</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,43; 8,84</t>
+          <t>-5,23; 8,76</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-20,21; 23,11</t>
+          <t>-21,05; 24,03</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-18,39; 28,61</t>
+          <t>-19,92; 25,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,71; 58,82</t>
+          <t>0,4; 57,41</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,89; 24,77</t>
+          <t>-11,63; 25,75</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-5,92; 8,69</t>
+          <t>-7,2; 8,53</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 9,85</t>
+          <t>-5,26; 10,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,97; 9,96</t>
+          <t>-6,02; 9,79</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,41; 7,93</t>
+          <t>-7,2; 7,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-22,11; 43,75</t>
+          <t>-24,57; 42,08</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-12,28; 34,11</t>
+          <t>-14,59; 34,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-13,87; 29,7</t>
+          <t>-14,57; 29,33</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-16,06; 21,35</t>
+          <t>-15,9; 19,15</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,92; 5,73</t>
+          <t>-9,34; 6,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-1,94; 13,94</t>
+          <t>-2,78; 12,66</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,09; 4,02</t>
+          <t>-10,56; 3,71</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-5,89; 31,4</t>
+          <t>-6,81; 33,06</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-23,76; 18,01</t>
+          <t>-22,12; 18,15</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-5,59; 54,89</t>
+          <t>-7,64; 48,96</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-30,12; 15,09</t>
+          <t>-31,39; 13,78</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,33; 114,8</t>
+          <t>-20,4; 122,79</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,45; 13,92</t>
+          <t>-7,8; 14,29</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,15; 16,28</t>
+          <t>-3,93; 16,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,09; 14,59</t>
+          <t>-7,38; 14,6</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,33; 5,93</t>
+          <t>-3,26; 5,87</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,79; 41,03</t>
+          <t>-16,61; 40,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 48,28</t>
+          <t>-8,55; 50,32</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,16; 25,25</t>
+          <t>-10,51; 25,9</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,68; 6,88</t>
+          <t>-3,49; 6,81</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 16,77</t>
+          <t>-3,41; 16,65</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,03; 16,97</t>
+          <t>0,99; 17,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-3,27; 14,36</t>
+          <t>-2,64; 15,28</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,27; 16,72</t>
+          <t>1,31; 17,23</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 88,99</t>
+          <t>-11,04; 84,57</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,44; 67,82</t>
+          <t>2,58; 69,12</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,73; 42,12</t>
+          <t>-6,22; 44,66</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,66; 43,81</t>
+          <t>2,65; 45,53</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,58; 8,76</t>
+          <t>-1,41; 9,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,03; 14,42</t>
+          <t>2,73; 14,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 5,99</t>
+          <t>-7,82; 6,49</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-40,66; -0,4</t>
+          <t>-41,74; -0,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 46,22</t>
+          <t>-5,58; 49,23</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,19; 52,93</t>
+          <t>7,84; 52,16</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-13,72; 13,1</t>
+          <t>-14,64; 13,97</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-65,61; -0,66</t>
+          <t>-67,42; -1,03</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,32; 4,14</t>
+          <t>-7,31; 3,73</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,64; 9,34</t>
+          <t>-0,63; 9,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,79; 7,0</t>
+          <t>-4,06; 7,04</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,61; 53,65</t>
+          <t>3,71; 50,68</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,45; 12,67</t>
+          <t>-19,36; 11,59</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-1,99; 38,36</t>
+          <t>-2,15; 38,03</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-8,84; 14,32</t>
+          <t>-7,49; 14,69</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,31; 275,99</t>
+          <t>5,47; 216,32</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 4,38</t>
+          <t>-0,92; 4,24</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,23; 7,35</t>
+          <t>2,26; 7,21</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 5,43</t>
+          <t>-0,07; 5,15</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 13,4</t>
+          <t>-6,45; 12,36</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,91; 15,35</t>
+          <t>-2,99; 14,75</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,15; 25,47</t>
+          <t>7,3; 25,27</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>0,0; 13,58</t>
+          <t>-0,16; 13,16</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,37; 29,22</t>
+          <t>-11,11; 26,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P19C01-Provincia-trans_bre.xlsx
+++ b/data/trans_bre/P19C01-Provincia-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,7</t>
+          <t>2,94</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>3,19%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,36; 17,76</t>
+          <t>-1,03; 17,28</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-8,66; 5,26</t>
+          <t>-8,4; 5,6</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-0,66; 15,97</t>
+          <t>-1,01; 15,42</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,45; 3,78</t>
+          <t>-0,06; 6,71</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-1,87; 76,02</t>
+          <t>-3,48; 77,93</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-39,58; 34,61</t>
+          <t>-39,13; 37,16</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-1,88; 80,56</t>
+          <t>-3,24; 79,89</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-2,54; 4,12</t>
+          <t>-0,07; 7,58</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1,63</t>
+          <t>1,7</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-7,02; 6,2</t>
+          <t>-6,49; 6,34</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 6,42</t>
+          <t>-6,79; 6,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 13,76</t>
+          <t>0,29; 14,28</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,23; 8,76</t>
+          <t>-4,3; 8,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-21,05; 24,03</t>
+          <t>-19,92; 23,82</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-19,92; 25,91</t>
+          <t>-20,63; 24,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,4; 57,41</t>
+          <t>0,67; 60,05</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-11,63; 25,75</t>
+          <t>-9,8; 24,28</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,03</t>
+          <t>0,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>1,05%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 8,53</t>
+          <t>-5,86; 9,46</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,26; 10,04</t>
+          <t>-4,65; 10,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-6,02; 9,79</t>
+          <t>-5,67; 9,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,2; 7,24</t>
+          <t>-6,96; 8,03</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-24,57; 42,08</t>
+          <t>-21,2; 47,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-14,59; 34,35</t>
+          <t>-12,57; 36,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-14,57; 29,33</t>
+          <t>-13,86; 29,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-15,9; 19,15</t>
+          <t>-15,73; 21,74</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,02</t>
+          <t>-0,4</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>21,39%</t>
+          <t>-1,22%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,34; 6,21</t>
+          <t>-9,93; 6,16</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-2,78; 12,66</t>
+          <t>-2,23; 13,77</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 3,71</t>
+          <t>-10,67; 3,22</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 33,06</t>
+          <t>-8,74; 7,26</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-22,12; 18,15</t>
+          <t>-24,0; 19,32</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-7,64; 48,96</t>
+          <t>-6,38; 54,92</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-31,39; 13,78</t>
+          <t>-31,19; 11,94</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-20,4; 122,79</t>
+          <t>-23,18; 25,82</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,06</t>
+          <t>3,11</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>3,57%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 14,29</t>
+          <t>-7,09; 13,77</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 16,94</t>
+          <t>-3,61; 17,24</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-7,38; 14,6</t>
+          <t>-7,81; 15,29</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-3,26; 5,87</t>
+          <t>-1,59; 8,03</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-16,61; 40,4</t>
+          <t>-16,06; 41,4</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-8,55; 50,32</t>
+          <t>-8,3; 51,54</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,51; 25,9</t>
+          <t>-11,03; 25,54</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-3,49; 6,81</t>
+          <t>-1,76; 9,55</t>
         </is>
       </c>
     </row>
@@ -1127,7 +1127,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>8,99</t>
+          <t>9,73</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1147,7 +1147,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>23,29%</t>
         </is>
       </c>
     </row>
@@ -1160,42 +1160,42 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-3,41; 16,65</t>
+          <t>-2,04; 16,18</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,99; 17,43</t>
+          <t>0,16; 17,27</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-2,64; 15,28</t>
+          <t>-3,73; 14,72</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1,31; 17,23</t>
+          <t>2,04; 16,51</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-11,04; 84,57</t>
+          <t>-7,34; 81,95</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,58; 69,12</t>
+          <t>0,41; 67,71</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 44,66</t>
+          <t>-8,79; 42,75</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>2,65; 45,53</t>
+          <t>4,19; 43,48</t>
         </is>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-16,63</t>
+          <t>-2,38</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>-27,87%</t>
+          <t>-4,04%</t>
         </is>
       </c>
     </row>
@@ -1260,42 +1260,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 9,33</t>
+          <t>-1,38; 9,43</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>2,73; 14,6</t>
+          <t>3,83; 14,78</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-7,82; 6,49</t>
+          <t>-7,78; 6,48</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-41,74; -0,72</t>
+          <t>-8,21; 2,66</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 49,23</t>
+          <t>-5,45; 48,93</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,84; 52,16</t>
+          <t>11,49; 53,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-14,64; 13,97</t>
+          <t>-14,25; 14,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>-67,42; -1,03</t>
+          <t>-13,26; 4,69</t>
         </is>
       </c>
     </row>
@@ -1327,7 +1327,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>23,71</t>
+          <t>5,81</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>47,38%</t>
+          <t>8,51%</t>
         </is>
       </c>
     </row>
@@ -1360,42 +1360,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-7,31; 3,73</t>
+          <t>-7,84; 4,02</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 9,52</t>
+          <t>-0,59; 9,51</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-4,06; 7,04</t>
+          <t>-4,17; 6,66</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>3,71; 50,68</t>
+          <t>1,48; 10,18</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-19,36; 11,59</t>
+          <t>-20,61; 12,55</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-2,15; 38,03</t>
+          <t>-2,04; 38,93</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-7,49; 14,69</t>
+          <t>-7,77; 13,56</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>5,47; 216,32</t>
+          <t>2,08; 15,97</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>2,43</t>
+          <t>2,07</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1447,7 +1447,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>3,63%</t>
         </is>
       </c>
     </row>
@@ -1460,42 +1460,42 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 4,24</t>
+          <t>-0,99; 4,32</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>2,26; 7,21</t>
+          <t>2,25; 7,22</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 5,15</t>
+          <t>-0,41; 5,22</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,45; 12,36</t>
+          <t>-0,4; 4,49</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-2,99; 14,75</t>
+          <t>-3,12; 15,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,3; 25,27</t>
+          <t>7,37; 25,7</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-0,16; 13,16</t>
+          <t>-0,96; 13,18</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-11,11; 26,99</t>
+          <t>-0,66; 8,03</t>
         </is>
       </c>
     </row>
